--- a/Day_03_excel.xlsx
+++ b/Day_03_excel.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f5c7b832c0e5f38/Documents/My projects/100-days-of-data-repository/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC1048A7095F46125ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72D2F6A-3702-49E4-9955-E69C52D5BCB4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,12 +20,245 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>SURNAME</t>
+  </si>
+  <si>
+    <t>SALARY</t>
+  </si>
+  <si>
+    <t>DEPARTMENT</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>20/447</t>
+  </si>
+  <si>
+    <t>21/229</t>
+  </si>
+  <si>
+    <t>34/229</t>
+  </si>
+  <si>
+    <t>22/234</t>
+  </si>
+  <si>
+    <t>19/204</t>
+  </si>
+  <si>
+    <t>27/291</t>
+  </si>
+  <si>
+    <t>36/668</t>
+  </si>
+  <si>
+    <t>20/225</t>
+  </si>
+  <si>
+    <t>18/403</t>
+  </si>
+  <si>
+    <t>26/678</t>
+  </si>
+  <si>
+    <t>21/450</t>
+  </si>
+  <si>
+    <t>24/993</t>
+  </si>
+  <si>
+    <t>30/420</t>
+  </si>
+  <si>
+    <t>27/203</t>
+  </si>
+  <si>
+    <t>29/235</t>
+  </si>
+  <si>
+    <t>38/208</t>
+  </si>
+  <si>
+    <t>22/104</t>
+  </si>
+  <si>
+    <t>11/207</t>
+  </si>
+  <si>
+    <t>OGBONOCHUKWU</t>
+  </si>
+  <si>
+    <t>ELLA</t>
+  </si>
+  <si>
+    <t>UDODI</t>
+  </si>
+  <si>
+    <t>CHUKWS</t>
+  </si>
+  <si>
+    <t>AGABELLA</t>
+  </si>
+  <si>
+    <t>AMARALLA</t>
+  </si>
+  <si>
+    <t>WHOES</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>BETHRAM</t>
+  </si>
+  <si>
+    <t>UWAEZU</t>
+  </si>
+  <si>
+    <t>IKEABALI</t>
+  </si>
+  <si>
+    <t>STANLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROONEY </t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>AKINTUMADE</t>
+  </si>
+  <si>
+    <t>DARASIMI</t>
+  </si>
+  <si>
+    <t>OLUFESOBI</t>
+  </si>
+  <si>
+    <t>MARTHA</t>
+  </si>
+  <si>
+    <t>OGHENETEGIRI</t>
+  </si>
+  <si>
+    <t>EMASOBA</t>
+  </si>
+  <si>
+    <t>ANYALE</t>
+  </si>
+  <si>
+    <t>FAUSTINE</t>
+  </si>
+  <si>
+    <t>UMAR</t>
+  </si>
+  <si>
+    <t>YAYAH</t>
+  </si>
+  <si>
+    <t>MALLAM</t>
+  </si>
+  <si>
+    <t>ABOKI</t>
+  </si>
+  <si>
+    <t>OKORAFEGA</t>
+  </si>
+  <si>
+    <t>OZABENAME</t>
+  </si>
+  <si>
+    <t>ADEADRCA</t>
+  </si>
+  <si>
+    <t>VIRAL</t>
+  </si>
+  <si>
+    <t>UCHE</t>
+  </si>
+  <si>
+    <t>AYOMIDE</t>
+  </si>
+  <si>
+    <t>SEGUN</t>
+  </si>
+  <si>
+    <t>OKONKWO</t>
+  </si>
+  <si>
+    <t>UMURAH</t>
+  </si>
+  <si>
+    <t>KELECHISO</t>
+  </si>
+  <si>
+    <t>AGABE.</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
+  </si>
+  <si>
+    <t>MARKETING</t>
+  </si>
+  <si>
+    <t>OPERATIONS</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>INTERN</t>
+  </si>
+  <si>
+    <t>MEDICAL</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>LEGAL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>CONTROL</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +569,474 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="17" width="18.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>70000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3">
+        <v>100000</v>
+      </c>
+      <c r="E3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>60000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>50000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>30000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7">
+        <v>700000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>250000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10">
+        <v>40000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11">
+        <v>90000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12">
+        <v>10000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13">
+        <v>5700000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14">
+        <v>23000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15">
+        <v>129500</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15">
+        <v>24</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16">
+        <v>1950340</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17">
+        <v>1284903</v>
+      </c>
+      <c r="E17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17">
+        <v>26</v>
+      </c>
+      <c r="G17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18">
+        <v>203480</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18">
+        <v>39</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19">
+        <v>600000</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19">
+        <v>59</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20">
+        <v>300003</v>
+      </c>
+      <c r="E20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>